--- a/backend/data/financials_by_company/1116.HK.xlsx
+++ b/backend/data/financials_by_company/1116.HK.xlsx
@@ -667,58 +667,52 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45473</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-872750</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
         <v>0.25</v>
       </c>
       <c r="D2" t="n">
-        <v>1314000</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-3491000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>-3491000</v>
-      </c>
+        <v>17064000</v>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
-        <v>-14629000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>5632000</v>
-      </c>
+        <v>-6255000</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>627021000</v>
+        <v>597136000</v>
       </c>
       <c r="J2" t="n">
-        <v>-2246000</v>
+        <v>17064000</v>
       </c>
       <c r="K2" t="n">
-        <v>-7878000</v>
+        <v>17064000</v>
       </c>
       <c r="L2" t="n">
-        <v>-2966000</v>
+        <v>-13995000</v>
       </c>
       <c r="M2" t="n">
-        <v>3590000</v>
+        <v>14604000</v>
       </c>
       <c r="N2" t="n">
-        <v>626000</v>
+        <v>609000</v>
       </c>
       <c r="O2" t="n">
-        <v>-11959000</v>
+        <v>-6255000</v>
       </c>
       <c r="P2" t="n">
-        <v>153272000</v>
+        <v>-6255000</v>
       </c>
       <c r="Q2" t="n">
-        <v>717261000</v>
+        <v>670741000</v>
       </c>
       <c r="R2" t="n">
-        <v>-7807000</v>
+        <v>17125000</v>
       </c>
       <c r="S2" t="n">
         <v>2158000000</v>
@@ -727,89 +721,83 @@
         <v>2158000000</v>
       </c>
       <c r="U2" t="n">
-        <v>0.07099999999999999</v>
+        <v>-0.0029</v>
       </c>
       <c r="V2" t="n">
-        <v>0.07099999999999999</v>
+        <v>-0.0029</v>
       </c>
       <c r="W2" t="n">
-        <v>153272000</v>
+        <v>-6255000</v>
       </c>
       <c r="X2" t="n">
-        <v>153272000</v>
+        <v>-6255000</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>153272000</v>
+        <v>-6255000</v>
       </c>
       <c r="AA2" t="n">
-        <v>139000</v>
+        <v>-3697000</v>
       </c>
       <c r="AB2" t="n">
-        <v>153133000</v>
+        <v>-2558000</v>
       </c>
       <c r="AC2" t="n">
-        <v>-14768000</v>
+        <v>-2558000</v>
       </c>
       <c r="AD2" t="n">
-        <v>3300000</v>
+        <v>5018000</v>
       </c>
       <c r="AE2" t="n">
-        <v>-11468000</v>
+        <v>2460000</v>
       </c>
       <c r="AF2" t="n">
-        <v>-69000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>-3491000</v>
-      </c>
+        <v>-4499000</v>
+      </c>
+      <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="n">
-        <v>3491000</v>
-      </c>
+      <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="n">
-        <v>-2966000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>2000</v>
-      </c>
+        <v>-13995000</v>
+      </c>
+      <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="n">
-        <v>3590000</v>
+        <v>14604000</v>
       </c>
       <c r="AM2" t="n">
-        <v>626000</v>
+        <v>609000</v>
       </c>
       <c r="AN2" t="n">
-        <v>-2853000</v>
+        <v>21015000</v>
       </c>
       <c r="AO2" t="n">
-        <v>90240000</v>
+        <v>73605000</v>
       </c>
       <c r="AP2" t="n">
-        <v>712000</v>
+        <v>2468000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>108938000</v>
+        <v>87954000</v>
       </c>
       <c r="AR2" t="n">
-        <v>63680000</v>
+        <v>43611000</v>
       </c>
       <c r="AS2" t="n">
-        <v>45258000</v>
+        <v>44343000</v>
       </c>
       <c r="AT2" t="n">
-        <v>87387000</v>
+        <v>94620000</v>
       </c>
       <c r="AU2" t="n">
-        <v>627021000</v>
+        <v>597136000</v>
       </c>
       <c r="AV2" t="n">
-        <v>714408000</v>
+        <v>691756000</v>
       </c>
       <c r="AW2" t="n">
-        <v>714408000</v>
+        <v>691756000</v>
       </c>
     </row>
     <row r="3">
@@ -963,52 +951,58 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44561</v>
+        <v>45473</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>-872750</v>
       </c>
       <c r="C4" t="n">
         <v>0.25</v>
       </c>
       <c r="D4" t="n">
-        <v>17064000</v>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+        <v>1314000</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-3491000</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-3491000</v>
+      </c>
       <c r="G4" t="n">
-        <v>-6255000</v>
-      </c>
-      <c r="H4" t="inlineStr"/>
+        <v>-14629000</v>
+      </c>
+      <c r="H4" t="n">
+        <v>5632000</v>
+      </c>
       <c r="I4" t="n">
-        <v>597136000</v>
+        <v>627021000</v>
       </c>
       <c r="J4" t="n">
-        <v>17064000</v>
+        <v>-2246000</v>
       </c>
       <c r="K4" t="n">
-        <v>17064000</v>
+        <v>-7878000</v>
       </c>
       <c r="L4" t="n">
-        <v>-13995000</v>
+        <v>-2966000</v>
       </c>
       <c r="M4" t="n">
-        <v>14604000</v>
+        <v>3590000</v>
       </c>
       <c r="N4" t="n">
-        <v>609000</v>
+        <v>626000</v>
       </c>
       <c r="O4" t="n">
-        <v>-6255000</v>
+        <v>-11959000</v>
       </c>
       <c r="P4" t="n">
-        <v>-6255000</v>
+        <v>153272000</v>
       </c>
       <c r="Q4" t="n">
-        <v>670741000</v>
+        <v>717261000</v>
       </c>
       <c r="R4" t="n">
-        <v>17125000</v>
+        <v>-7807000</v>
       </c>
       <c r="S4" t="n">
         <v>2158000000</v>
@@ -1017,83 +1011,89 @@
         <v>2158000000</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0029</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.0029</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="W4" t="n">
-        <v>-6255000</v>
+        <v>153272000</v>
       </c>
       <c r="X4" t="n">
-        <v>-6255000</v>
+        <v>153272000</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>-6255000</v>
+        <v>153272000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-3697000</v>
+        <v>139000</v>
       </c>
       <c r="AB4" t="n">
-        <v>-2558000</v>
+        <v>153133000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-2558000</v>
+        <v>-14768000</v>
       </c>
       <c r="AD4" t="n">
-        <v>5018000</v>
+        <v>3300000</v>
       </c>
       <c r="AE4" t="n">
-        <v>2460000</v>
+        <v>-11468000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-4499000</v>
-      </c>
-      <c r="AG4" t="inlineStr"/>
+        <v>-69000</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>-3491000</v>
+      </c>
       <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr"/>
+      <c r="AI4" t="n">
+        <v>3491000</v>
+      </c>
       <c r="AJ4" t="n">
-        <v>-13995000</v>
-      </c>
-      <c r="AK4" t="inlineStr"/>
+        <v>-2966000</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>2000</v>
+      </c>
       <c r="AL4" t="n">
-        <v>14604000</v>
+        <v>3590000</v>
       </c>
       <c r="AM4" t="n">
-        <v>609000</v>
+        <v>626000</v>
       </c>
       <c r="AN4" t="n">
-        <v>21015000</v>
+        <v>-2853000</v>
       </c>
       <c r="AO4" t="n">
-        <v>73605000</v>
+        <v>90240000</v>
       </c>
       <c r="AP4" t="n">
-        <v>2468000</v>
+        <v>712000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>87954000</v>
+        <v>108938000</v>
       </c>
       <c r="AR4" t="n">
-        <v>43611000</v>
+        <v>63680000</v>
       </c>
       <c r="AS4" t="n">
-        <v>44343000</v>
+        <v>45258000</v>
       </c>
       <c r="AT4" t="n">
-        <v>94620000</v>
+        <v>87387000</v>
       </c>
       <c r="AU4" t="n">
-        <v>597136000</v>
+        <v>627021000</v>
       </c>
       <c r="AV4" t="n">
-        <v>691756000</v>
+        <v>714408000</v>
       </c>
       <c r="AW4" t="n">
-        <v>691756000</v>
+        <v>714408000</v>
       </c>
     </row>
   </sheetData>
@@ -1404,7 +1404,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45473</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
         <v>2158000000</v>
@@ -1413,47 +1413,43 @@
         <v>2158000000</v>
       </c>
       <c r="D2" t="n">
-        <v>42468000</v>
+        <v>183333000</v>
       </c>
       <c r="E2" t="n">
-        <v>100350000</v>
+        <v>219273000</v>
       </c>
       <c r="F2" t="n">
-        <v>215522000</v>
+        <v>430100000</v>
       </c>
       <c r="G2" t="n">
-        <v>315522000</v>
+        <v>648381000</v>
       </c>
       <c r="H2" t="n">
-        <v>196327000</v>
+        <v>220445000</v>
       </c>
       <c r="I2" t="n">
-        <v>215522000</v>
+        <v>430100000</v>
       </c>
       <c r="J2" t="n">
-        <v>350000</v>
+        <v>992000</v>
       </c>
       <c r="K2" t="n">
-        <v>215522000</v>
+        <v>430100000</v>
       </c>
       <c r="L2" t="n">
-        <v>215522000</v>
+        <v>430100000</v>
       </c>
       <c r="M2" t="n">
-        <v>282127000</v>
+        <v>492006000</v>
       </c>
       <c r="N2" t="n">
-        <v>66605000</v>
+        <v>61906000</v>
       </c>
       <c r="O2" t="n">
-        <v>215522000</v>
-      </c>
-      <c r="P2" t="n">
-        <v>-454186000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>213309000</v>
-      </c>
+        <v>430100000</v>
+      </c>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="n">
         <v>391760000</v>
       </c>
@@ -1461,120 +1457,92 @@
         <v>391760000</v>
       </c>
       <c r="T2" t="n">
-        <v>286432000</v>
+        <v>338982000</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>97000</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>97000</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>97000</v>
       </c>
       <c r="X2" t="n">
-        <v>286432000</v>
+        <v>338885000</v>
       </c>
       <c r="Y2" t="n">
-        <v>100350000</v>
+        <v>219176000</v>
       </c>
       <c r="Z2" t="n">
-        <v>350000</v>
+        <v>895000</v>
       </c>
       <c r="AA2" t="n">
-        <v>100000000</v>
+        <v>218281000</v>
       </c>
       <c r="AB2" t="n">
-        <v>167027000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>63385000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>2681000</v>
-      </c>
+        <v>119709000</v>
+      </c>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="n">
-        <v>14912000</v>
+        <v>12588000</v>
       </c>
       <c r="AF2" t="n">
-        <v>86049000</v>
+        <v>107121000</v>
       </c>
       <c r="AG2" t="n">
-        <v>568559000</v>
+        <v>830988000</v>
       </c>
       <c r="AH2" t="n">
-        <v>85800000</v>
+        <v>271658000</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>209274000</v>
       </c>
       <c r="AJ2" t="n">
         <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>209274000</v>
       </c>
       <c r="AL2" t="n">
-        <v>85800000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>-120324000</v>
-      </c>
+        <v>62384000</v>
+      </c>
+      <c r="AM2" t="inlineStr"/>
       <c r="AN2" t="n">
-        <v>206124000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>36396000</v>
-      </c>
-      <c r="AP2" t="inlineStr"/>
-      <c r="AQ2" t="n">
-        <v>105979000</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>63749000</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>43511000</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>0</v>
-      </c>
+        <v>62384000</v>
+      </c>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="n">
+        <v>62384000</v>
+      </c>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
       <c r="AU2" t="n">
-        <v>482759000</v>
+        <v>559330000</v>
       </c>
       <c r="AV2" t="inlineStr"/>
-      <c r="AW2" t="n">
-        <v>56712000</v>
-      </c>
+      <c r="AW2" t="inlineStr"/>
       <c r="AX2" t="n">
-        <v>79307000</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>43100000</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>716000</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>35491000</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>20426000</v>
-      </c>
+        <v>111578000</v>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="inlineStr"/>
       <c r="BC2" t="n">
-        <v>268782000</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>-2436000</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>271218000</v>
-      </c>
+        <v>412804000</v>
+      </c>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr"/>
       <c r="BF2" t="n">
-        <v>57532000</v>
+        <v>34948000</v>
       </c>
       <c r="BG2" t="n">
-        <v>57532000</v>
+        <v>34948000</v>
       </c>
     </row>
     <row r="3">
@@ -1756,7 +1724,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44561</v>
+        <v>45473</v>
       </c>
       <c r="B4" t="n">
         <v>2158000000</v>
@@ -1765,43 +1733,47 @@
         <v>2158000000</v>
       </c>
       <c r="D4" t="n">
-        <v>183333000</v>
+        <v>42468000</v>
       </c>
       <c r="E4" t="n">
-        <v>219273000</v>
+        <v>100350000</v>
       </c>
       <c r="F4" t="n">
-        <v>430100000</v>
+        <v>215522000</v>
       </c>
       <c r="G4" t="n">
-        <v>648381000</v>
+        <v>315522000</v>
       </c>
       <c r="H4" t="n">
-        <v>220445000</v>
+        <v>196327000</v>
       </c>
       <c r="I4" t="n">
-        <v>430100000</v>
+        <v>215522000</v>
       </c>
       <c r="J4" t="n">
-        <v>992000</v>
+        <v>350000</v>
       </c>
       <c r="K4" t="n">
-        <v>430100000</v>
+        <v>215522000</v>
       </c>
       <c r="L4" t="n">
-        <v>430100000</v>
+        <v>215522000</v>
       </c>
       <c r="M4" t="n">
-        <v>492006000</v>
+        <v>282127000</v>
       </c>
       <c r="N4" t="n">
-        <v>61906000</v>
+        <v>66605000</v>
       </c>
       <c r="O4" t="n">
-        <v>430100000</v>
-      </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
+        <v>215522000</v>
+      </c>
+      <c r="P4" t="n">
+        <v>-454186000</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>213309000</v>
+      </c>
       <c r="R4" t="n">
         <v>391760000</v>
       </c>
@@ -1809,92 +1781,120 @@
         <v>391760000</v>
       </c>
       <c r="T4" t="n">
-        <v>338982000</v>
+        <v>286432000</v>
       </c>
       <c r="U4" t="n">
-        <v>97000</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>97000</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>97000</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>338885000</v>
+        <v>286432000</v>
       </c>
       <c r="Y4" t="n">
-        <v>219176000</v>
+        <v>100350000</v>
       </c>
       <c r="Z4" t="n">
-        <v>895000</v>
+        <v>350000</v>
       </c>
       <c r="AA4" t="n">
-        <v>218281000</v>
+        <v>100000000</v>
       </c>
       <c r="AB4" t="n">
-        <v>119709000</v>
-      </c>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
+        <v>167027000</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>63385000</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>2681000</v>
+      </c>
       <c r="AE4" t="n">
-        <v>12588000</v>
+        <v>14912000</v>
       </c>
       <c r="AF4" t="n">
-        <v>107121000</v>
+        <v>86049000</v>
       </c>
       <c r="AG4" t="n">
-        <v>830988000</v>
+        <v>568559000</v>
       </c>
       <c r="AH4" t="n">
-        <v>271658000</v>
+        <v>85800000</v>
       </c>
       <c r="AI4" t="n">
-        <v>209274000</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
         <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>209274000</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>62384000</v>
-      </c>
-      <c r="AM4" t="inlineStr"/>
+        <v>85800000</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>-120324000</v>
+      </c>
       <c r="AN4" t="n">
-        <v>62384000</v>
-      </c>
-      <c r="AO4" t="inlineStr"/>
-      <c r="AP4" t="n">
-        <v>62384000</v>
-      </c>
-      <c r="AQ4" t="inlineStr"/>
-      <c r="AR4" t="inlineStr"/>
-      <c r="AS4" t="inlineStr"/>
-      <c r="AT4" t="inlineStr"/>
+        <v>206124000</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>36396000</v>
+      </c>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="n">
+        <v>105979000</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>63749000</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>43511000</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0</v>
+      </c>
       <c r="AU4" t="n">
-        <v>559330000</v>
+        <v>482759000</v>
       </c>
       <c r="AV4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr"/>
+      <c r="AW4" t="n">
+        <v>56712000</v>
+      </c>
       <c r="AX4" t="n">
-        <v>111578000</v>
-      </c>
-      <c r="AY4" t="inlineStr"/>
-      <c r="AZ4" t="inlineStr"/>
-      <c r="BA4" t="inlineStr"/>
-      <c r="BB4" t="inlineStr"/>
+        <v>79307000</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>43100000</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>716000</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>35491000</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>20426000</v>
+      </c>
       <c r="BC4" t="n">
-        <v>412804000</v>
-      </c>
-      <c r="BD4" t="inlineStr"/>
-      <c r="BE4" t="inlineStr"/>
+        <v>268782000</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>-2436000</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>271218000</v>
+      </c>
       <c r="BF4" t="n">
-        <v>34948000</v>
+        <v>57532000</v>
       </c>
       <c r="BG4" t="n">
-        <v>34948000</v>
+        <v>57532000</v>
       </c>
     </row>
   </sheetData>
@@ -2095,106 +2095,88 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45473</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-13453000</v>
+        <v>-39773000</v>
       </c>
       <c r="C2" t="n">
-        <v>-75000000</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>100000000</v>
+        <v>44254000</v>
       </c>
       <c r="E2" t="n">
-        <v>-28183000</v>
+        <v>-14381000</v>
       </c>
       <c r="F2" t="n">
-        <v>57532000</v>
+        <v>34948000</v>
       </c>
       <c r="G2" t="n">
-        <v>46376000</v>
+        <v>37575000</v>
       </c>
       <c r="H2" t="n">
-        <v>1330000</v>
+        <v>-3061000</v>
       </c>
       <c r="I2" t="n">
-        <v>9826000</v>
+        <v>434000</v>
       </c>
       <c r="J2" t="n">
-        <v>21177000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>200000</v>
-      </c>
+        <v>39852000</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>-3592000</v>
+        <v>-3178000</v>
       </c>
       <c r="M2" t="n">
-        <v>25000000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>25000000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>-75000000</v>
-      </c>
-      <c r="P2" t="n">
-        <v>100000000</v>
-      </c>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
+        <v>44254000</v>
+      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="n">
+        <v>44254000</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>44254000</v>
+      </c>
       <c r="T2" t="n">
-        <v>-26081000</v>
+        <v>-14026000</v>
       </c>
       <c r="U2" t="n">
-        <v>626000</v>
-      </c>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
       <c r="X2" t="n">
-        <v>-26697000</v>
+        <v>-14026000</v>
       </c>
       <c r="Y2" t="n">
-        <v>1486000</v>
+        <v>355000</v>
       </c>
       <c r="Z2" t="n">
-        <v>-28183000</v>
+        <v>-14381000</v>
       </c>
       <c r="AA2" t="n">
-        <v>14730000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>-793000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>15077000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>48452000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>12581000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>-45956000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>2966000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>5632000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>5632000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>156433000</v>
-      </c>
+        <v>-25392000</v>
+      </c>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -2299,88 +2281,106 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44561</v>
+        <v>45473</v>
       </c>
       <c r="B4" t="n">
-        <v>-39773000</v>
+        <v>-13453000</v>
       </c>
       <c r="C4" t="n">
+        <v>-75000000</v>
+      </c>
+      <c r="D4" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-28183000</v>
+      </c>
+      <c r="F4" t="n">
+        <v>57532000</v>
+      </c>
+      <c r="G4" t="n">
+        <v>46376000</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1330000</v>
+      </c>
+      <c r="I4" t="n">
+        <v>9826000</v>
+      </c>
+      <c r="J4" t="n">
+        <v>21177000</v>
+      </c>
+      <c r="K4" t="n">
+        <v>200000</v>
+      </c>
+      <c r="L4" t="n">
+        <v>-3592000</v>
+      </c>
+      <c r="M4" t="n">
+        <v>25000000</v>
+      </c>
+      <c r="N4" t="n">
+        <v>25000000</v>
+      </c>
+      <c r="O4" t="n">
+        <v>-75000000</v>
+      </c>
+      <c r="P4" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="n">
+        <v>-26081000</v>
+      </c>
+      <c r="U4" t="n">
+        <v>626000</v>
+      </c>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="n">
+        <v>-26697000</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1486000</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>-28183000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>14730000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>-793000</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>15077000</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>48452000</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>12581000</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>-45956000</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>2966000</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>5632000</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>5632000</v>
+      </c>
+      <c r="AJ4" t="n">
         <v>0</v>
       </c>
-      <c r="D4" t="n">
-        <v>44254000</v>
-      </c>
-      <c r="E4" t="n">
-        <v>-14381000</v>
-      </c>
-      <c r="F4" t="n">
-        <v>34948000</v>
-      </c>
-      <c r="G4" t="n">
-        <v>37575000</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-3061000</v>
-      </c>
-      <c r="I4" t="n">
-        <v>434000</v>
-      </c>
-      <c r="J4" t="n">
-        <v>39852000</v>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="n">
-        <v>-3178000</v>
-      </c>
-      <c r="M4" t="n">
-        <v>44254000</v>
-      </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="n">
-        <v>44254000</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>44254000</v>
-      </c>
-      <c r="T4" t="n">
-        <v>-14026000</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>-14026000</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>355000</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>-14381000</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>-25392000</v>
-      </c>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr"/>
-      <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr"/>
-      <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr"/>
+      <c r="AK4" t="n">
+        <v>156433000</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2919,197 +2919,197 @@
       </c>
       <c r="DA1" t="inlineStr">
         <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
           <t>shortName</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="DC1" t="inlineStr">
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
         <is>
           <t>corporateActions</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="DK1" t="inlineStr">
         <is>
           <t>regularMarketTime</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
+      <c r="DL1" t="inlineStr">
         <is>
           <t>exchange</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
+      <c r="DM1" t="inlineStr">
         <is>
           <t>messageBoardId</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="DN1" t="inlineStr">
         <is>
           <t>exchangeTimezoneName</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="DO1" t="inlineStr">
         <is>
           <t>exchangeTimezoneShortName</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
+      <c r="DP1" t="inlineStr">
         <is>
           <t>gmtOffSetMilliseconds</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
+      <c r="DQ1" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
+      <c r="DR1" t="inlineStr">
         <is>
           <t>esgPopulated</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>prevName</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>nameChangeDate</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
         <is>
           <t>fullExchangeName</t>
         </is>
       </c>
-      <c r="DS1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>averageDailyVolume3Month</t>
         </is>
       </c>
-      <c r="DT1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChange</t>
         </is>
       </c>
-      <c r="DU1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChangePercent</t>
         </is>
       </c>
-      <c r="DV1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekRange</t>
         </is>
       </c>
-      <c r="DW1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChange</t>
         </is>
       </c>
-      <c r="DX1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChangePercent</t>
         </is>
       </c>
-      <c r="DY1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekChangePercent</t>
         </is>
       </c>
-      <c r="DZ1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>earningsTimestampStart</t>
         </is>
       </c>
-      <c r="EA1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>earningsTimestampEnd</t>
         </is>
       </c>
-      <c r="EB1" t="inlineStr">
+      <c r="EH1" t="inlineStr">
         <is>
           <t>isEarningsDateEstimate</t>
         </is>
       </c>
-      <c r="EC1" t="inlineStr">
+      <c r="EI1" t="inlineStr">
         <is>
           <t>epsTrailingTwelveMonths</t>
         </is>
       </c>
-      <c r="ED1" t="inlineStr">
+      <c r="EJ1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChange</t>
         </is>
       </c>
-      <c r="EE1" t="inlineStr">
+      <c r="EK1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="EF1" t="inlineStr">
+      <c r="EL1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChange</t>
         </is>
       </c>
-      <c r="EG1" t="inlineStr">
+      <c r="EM1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>prevName</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>nameChangeDate</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>longName</t>
         </is>
       </c>
       <c r="EN1" t="inlineStr">
@@ -3194,7 +3194,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Dr. Yun Kit  Ip', 'age': 64, 'title': 'Executive Chairman', 'yearBorn': 1961, 'fiscalYear': 2025, 'totalPay': 646410, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Yana  Zhang', 'age': 37, 'title': 'CFO &amp; Executive Director', 'yearBorn': 1988, 'fiscalYear': 2025, 'totalPay': 612815, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Prof. Ka Yue  Cheung', 'age': 53, 'title': 'Executive Director', 'yearBorn': 1972, 'fiscalYear': 2025, 'totalPay': 494654, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Yiu Kuen  Tai', 'age': 58, 'title': 'Chief Executive Officer', 'yearBorn': 1967, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Yiu Cho  Leung', 'age': 45, 'title': 'Company Secretary', 'yearBorn': 1980, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Dr. Yun Kit  Ip', 'age': 64, 'title': 'Executive Chairman', 'yearBorn': 1961, 'fiscalYear': 2025, 'totalPay': 645895, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Yana  Zhang', 'age': 37, 'title': 'CFO &amp; Executive Director', 'yearBorn': 1988, 'fiscalYear': 2025, 'totalPay': 612327, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Prof. Ka Yue  Cheung', 'age': 53, 'title': 'Executive Director', 'yearBorn': 1972, 'fiscalYear': 2025, 'totalPay': 494260, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Yiu Kuen  Tai', 'age': 58, 'title': 'Chief Executive Officer', 'yearBorn': 1967, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Yiu Cho  Leung', 'age': 45, 'title': 'Company Secretary', 'yearBorn': 1980, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -3212,28 +3212,28 @@
         <v>3</v>
       </c>
       <c r="U2" t="n">
-        <v>0.24</v>
+        <v>0.226</v>
       </c>
       <c r="V2" t="n">
-        <v>0.24</v>
+        <v>0.222</v>
       </c>
       <c r="W2" t="n">
-        <v>0.24</v>
+        <v>0.205</v>
       </c>
       <c r="X2" t="n">
-        <v>0.25</v>
+        <v>0.222</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.24</v>
+        <v>0.226</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.24</v>
+        <v>0.222</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.24</v>
+        <v>0.205</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.25</v>
+        <v>0.222</v>
       </c>
       <c r="AC2" t="n">
         <v>1212105600</v>
@@ -3242,28 +3242,28 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>-1.019</v>
+        <v>-1.021</v>
       </c>
       <c r="AF2" t="n">
-        <v>180000</v>
+        <v>1330000</v>
       </c>
       <c r="AG2" t="n">
-        <v>180000</v>
+        <v>1330000</v>
       </c>
       <c r="AH2" t="n">
-        <v>210866</v>
+        <v>202915</v>
       </c>
       <c r="AI2" t="n">
-        <v>113333</v>
+        <v>354000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>113333</v>
+        <v>354000</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.24</v>
+        <v>0.207</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.244</v>
+        <v>0.22</v>
       </c>
       <c r="AM2" t="n">
         <v>0</v>
@@ -3272,16 +3272,16 @@
         <v>0</v>
       </c>
       <c r="AO2" t="n">
-        <v>526552032</v>
+        <v>459654016</v>
       </c>
       <c r="AP2" t="n">
-        <v>517920000</v>
+        <v>487708000</v>
       </c>
       <c r="AQ2" t="n">
         <v>0.188</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.4</v>
+        <v>0.395</v>
       </c>
       <c r="AS2" t="n">
         <v>2.551219</v>
@@ -3290,13 +3290,13 @@
         <v>0.121</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.64299214</v>
+        <v>0.5613005</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.25</v>
+        <v>0.2451</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.285105</v>
+        <v>0.28447</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
@@ -3313,7 +3313,7 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>697987968</v>
+        <v>631089984</v>
       </c>
       <c r="BC2" t="n">
         <v>-0.05824</v>
@@ -3334,10 +3334,10 @@
         <v>2158000000</v>
       </c>
       <c r="BI2" t="n">
-        <v>0.10308431</v>
+        <v>0.10301992</v>
       </c>
       <c r="BJ2" t="n">
-        <v>2.3669946</v>
+        <v>2.0675611</v>
       </c>
       <c r="BK2" t="n">
         <v>1751241600</v>
@@ -3363,16 +3363,16 @@
         <v>1539648000</v>
       </c>
       <c r="BR2" t="n">
-        <v>0.852</v>
+        <v>0.771</v>
       </c>
       <c r="BS2" t="n">
-        <v>-23.082</v>
+        <v>-20.87</v>
       </c>
       <c r="BT2" t="n">
-        <v>-0.38461536</v>
+        <v>-0.27096772</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.27294624</v>
+        <v>0.24487448</v>
       </c>
       <c r="BV2" t="n">
         <v>0.034016</v>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="BY2" t="n">
-        <v>0.244</v>
+        <v>0.213</v>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
@@ -3487,148 +3487,148 @@
       </c>
       <c r="DA2" t="inlineStr">
         <is>
+          <t>Huiyuan Cowins Technology Group Limited</t>
+        </is>
+      </c>
+      <c r="DB2" t="n">
+        <v>-5.752211</v>
+      </c>
+      <c r="DC2" t="n">
+        <v>0.213</v>
+      </c>
+      <c r="DD2" t="inlineStr">
+        <is>
+          <t>PRE</t>
+        </is>
+      </c>
+      <c r="DE2" t="inlineStr">
+        <is>
           <t>HC TECH GP</t>
         </is>
       </c>
-      <c r="DB2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="DC2" t="inlineStr">
+      <c r="DF2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DG2" t="n">
+        <v>1087781400000</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>-0.012999997</v>
+      </c>
+      <c r="DI2" t="inlineStr">
+        <is>
+          <t>0.205 - 0.222</t>
+        </is>
+      </c>
+      <c r="DJ2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="DD2" t="n">
-        <v>1780367653</v>
-      </c>
-      <c r="DE2" t="n">
-        <v>1.6666701</v>
-      </c>
-      <c r="DF2" t="n">
-        <v>0.244</v>
-      </c>
-      <c r="DG2" t="inlineStr">
+      <c r="DK2" t="n">
+        <v>1782114990</v>
+      </c>
+      <c r="DL2" t="inlineStr">
         <is>
           <t>HKG</t>
         </is>
       </c>
-      <c r="DH2" t="inlineStr">
+      <c r="DM2" t="inlineStr">
         <is>
           <t>finmb_11016349</t>
         </is>
       </c>
-      <c r="DI2" t="inlineStr">
+      <c r="DN2" t="inlineStr">
         <is>
           <t>Asia/Hong_Kong</t>
         </is>
       </c>
-      <c r="DJ2" t="inlineStr">
+      <c r="DO2" t="inlineStr">
         <is>
           <t>HKT</t>
         </is>
       </c>
-      <c r="DK2" t="n">
+      <c r="DP2" t="n">
         <v>28800000</v>
       </c>
-      <c r="DL2" t="inlineStr">
+      <c r="DQ2" t="inlineStr">
         <is>
           <t>hk_market</t>
         </is>
       </c>
-      <c r="DM2" t="b">
+      <c r="DR2" t="b">
         <v>0</v>
       </c>
-      <c r="DN2" t="b">
+      <c r="DS2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DU2" t="inlineStr">
+        <is>
+          <t>Mayer Holdings Limited</t>
+        </is>
+      </c>
+      <c r="DV2" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="DW2" t="b">
         <v>0</v>
       </c>
-      <c r="DO2" t="n">
-        <v>1087781400000</v>
-      </c>
-      <c r="DP2" t="n">
-        <v>0.004000008</v>
-      </c>
-      <c r="DQ2" t="inlineStr">
-        <is>
-          <t>0.24 - 0.25</t>
-        </is>
-      </c>
-      <c r="DR2" t="inlineStr">
+      <c r="DX2" t="inlineStr">
         <is>
           <t>HKSE</t>
         </is>
       </c>
-      <c r="DS2" t="n">
-        <v>210866</v>
-      </c>
-      <c r="DT2" t="n">
-        <v>0.05600001</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>0.2978724</v>
-      </c>
-      <c r="DV2" t="inlineStr">
-        <is>
-          <t>0.188 - 0.4</t>
-        </is>
-      </c>
-      <c r="DW2" t="n">
-        <v>-0.156</v>
-      </c>
-      <c r="DX2" t="n">
-        <v>-0.39000002</v>
-      </c>
       <c r="DY2" t="n">
-        <v>-38.461536</v>
+        <v>202915</v>
       </c>
       <c r="DZ2" t="n">
+        <v>0.025000006</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>0.13297875</v>
+      </c>
+      <c r="EB2" t="inlineStr">
+        <is>
+          <t>0.188 - 0.395</t>
+        </is>
+      </c>
+      <c r="EC2" t="n">
+        <v>-0.18200001</v>
+      </c>
+      <c r="ED2" t="n">
+        <v>-0.46075952</v>
+      </c>
+      <c r="EE2" t="n">
+        <v>-27.096771</v>
+      </c>
+      <c r="EF2" t="n">
         <v>1743026768</v>
       </c>
-      <c r="EA2" t="n">
+      <c r="EG2" t="n">
         <v>1743026768</v>
       </c>
-      <c r="EB2" t="b">
+      <c r="EH2" t="b">
         <v>0</v>
       </c>
-      <c r="EC2" t="n">
+      <c r="EI2" t="n">
         <v>-0.03</v>
       </c>
-      <c r="ED2" t="n">
-        <v>-0.0059999973</v>
-      </c>
-      <c r="EE2" t="n">
-        <v>-0.023999989</v>
-      </c>
-      <c r="EF2" t="n">
-        <v>-0.041104987</v>
-      </c>
-      <c r="EG2" t="n">
-        <v>-0.14417492</v>
-      </c>
-      <c r="EH2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EI2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EJ2" t="inlineStr">
-        <is>
-          <t>Mayer Holdings Limited</t>
-        </is>
-      </c>
-      <c r="EK2" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="EL2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EM2" t="inlineStr">
-        <is>
-          <t>Huiyuan Cowins Technology Group Limited</t>
-        </is>
+      <c r="EJ2" t="n">
+        <v>-0.032100007</v>
+      </c>
+      <c r="EK2" t="n">
+        <v>-0.13096698</v>
+      </c>
+      <c r="EL2" t="n">
+        <v>-0.07146999</v>
+      </c>
+      <c r="EM2" t="n">
+        <v>-0.25123912</v>
       </c>
       <c r="EN2" t="inlineStr"/>
     </row>
